--- a/business_forms/035_product_giveaway_entry_form--business_forms.xlsx
+++ b/business_forms/035_product_giveaway_entry_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'New Hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'New Jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'new_mexico'}</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'New Mexico'}</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'North Carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'North Dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Rhode Island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'south_carolina'}</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'South Carolina'}</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'south_dakota'}</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'South Dakota'}</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'west_virginia'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'West Virginia'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'wisconsin'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Wisconsin'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'wyoming'}</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Wyoming'}</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
